--- a/plate3d/PLATE3D_SHOE.xlsx
+++ b/plate3d/PLATE3D_SHOE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
   <si>
     <t>EMBEDDED BASE / LEVELLING SHOE - every plate at its scheduled size, thickness and count</t>
   </si>
@@ -302,6 +302,27 @@
   </si>
   <si>
     <t>ADD</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>SHOE - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -698,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="66" customWidth="1"/>
@@ -1054,6 +1075,7 @@
         <v>240</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>19</v>
@@ -1094,6 +1116,7 @@
         <v>135</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
@@ -1226,6 +1249,7 @@
         <v>115</v>
       </c>
     </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>48</v>
@@ -1506,6 +1530,7 @@
         <v>41</v>
       </c>
     </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>19</v>
@@ -1924,6 +1949,7 @@
         <v>90</v>
       </c>
     </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>19</v>
@@ -2076,6 +2102,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>19</v>
@@ -2260,6 +2287,7 @@
         <v>415</v>
       </c>
     </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>19</v>
@@ -2318,6 +2346,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>87</v>
@@ -2370,16 +2399,50 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67" s="3" t="s">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>97</v>
+      </c>
+      <c r="C67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D67" t="s">
+        <v>98</v>
+      </c>
+      <c r="G67">
+        <v>50</v>
+      </c>
+      <c r="H67" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" t="s">
+        <v>102</v>
+      </c>
+      <c r="E68">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_SHOE.xlsx
+++ b/plate3d/PLATE3D_SHOE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="98">
   <si>
     <t>EMBEDDED BASE / LEVELLING SHOE - every plate at its scheduled size, thickness and count</t>
   </si>
@@ -302,27 +302,6 @@
   </si>
   <si>
     <t>ADD</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>SHOE - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -719,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="66" customWidth="1"/>
@@ -1075,7 +1054,6 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>19</v>
@@ -1116,7 +1094,6 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
@@ -1249,7 +1226,6 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>48</v>
@@ -1530,7 +1506,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>19</v>
@@ -1949,7 +1924,6 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>19</v>
@@ -2102,7 +2076,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>19</v>
@@ -2287,7 +2260,6 @@
         <v>415</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>19</v>
@@ -2346,7 +2318,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>87</v>
@@ -2399,50 +2370,16 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" t="s">
-        <v>98</v>
-      </c>
-      <c r="G67">
-        <v>50</v>
-      </c>
-      <c r="H67" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" t="s">
-        <v>101</v>
-      </c>
-      <c r="D68" t="s">
-        <v>102</v>
-      </c>
-      <c r="E68">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>